--- a/파이썬/코딩교실 매크로/3.코딩교실마감/만족도조사/만족도조사.xlsx
+++ b/파이썬/코딩교실 매크로/3.코딩교실마감/만족도조사/만족도조사.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\3.코딩교실마감\만족도조사\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\3.코딩교실마감\만족도조사\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B723CB-4778-487E-A620-341F9A602173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EFEC7F-6AB2-4FD8-AED5-615C50F8D942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52785" yWindow="990" windowWidth="22140" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -412,12 +412,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="O1:P9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O1" t="s">
         <v>0</v>
       </c>
@@ -425,15 +425,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O2" t="s">
         <v>3</v>
       </c>
       <c r="P2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="15:16" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O3" t="s">
         <v>1</v>
       </c>
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O4" t="s">
         <v>2</v>
       </c>
@@ -449,7 +449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O5">
         <v>1</v>
       </c>
@@ -457,7 +457,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O6">
         <v>2</v>
       </c>
@@ -465,7 +465,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O7">
         <v>3</v>
       </c>
@@ -473,7 +473,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="8" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O8">
         <v>4</v>
       </c>
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="15:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="15:16" x14ac:dyDescent="0.4">
       <c r="O9">
         <v>5</v>
       </c>
